--- a/GameDesign/Excel/DropCommon.xlsx
+++ b/GameDesign/Excel/DropCommon.xlsx
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1168,7 +1168,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,678 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>200101</v>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv1 흙 묻은 유물 — 판정당 1% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>200102</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv1 조개 박힌 유물 — 판정당 0.15% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>200103</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv1 산호 엉긴 유물 — 판정당 0.015% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="19" t="n">
+        <v>200201</v>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv2 흙 묻은 유물 — 판정당 0.8% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="19" t="n">
+        <v>200202</v>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv2 조개 박힌 유물 — 판정당 0.3% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="19" t="n">
+        <v>200203</v>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv2 산호 엉긴 유물 — 판정당 0.05% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="19" t="n">
+        <v>200204</v>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>100064</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv2 봉인된 유물 — 판정당 0.005% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="19" t="n">
+        <v>200301</v>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv3 흙 묻은 유물 — 판정당 0.6% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="19" t="n">
+        <v>200302</v>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv3 조개 박힌 유물 — 판정당 0.4% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="19" t="n">
+        <v>200303</v>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv3 산호 엉긴 유물 — 판정당 0.15% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="19" t="n">
+        <v>200304</v>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>100064</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv3 봉인된 유물 — 판정당 0.015% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="19" t="n">
+        <v>200305</v>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv3 황금 띠 유물 — 판정당 0.0015% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="19" t="n">
+        <v>200401</v>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 흙 묻은 유물 — 판정당 0.4% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="19" t="n">
+        <v>200402</v>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 조개 박힌 유물 — 판정당 0.5% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="19" t="n">
+        <v>200403</v>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 산호 엉긴 유물 — 판정당 0.25% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="19" t="n">
+        <v>200404</v>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>100064</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 봉인된 유물 — 판정당 0.05% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="19" t="n">
+        <v>200405</v>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 황금 띠 유물 — 판정당 0.005% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="19" t="n">
+        <v>200406</v>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>100066</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv4 왕의 유물 — 판정당 0.0005% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="19" t="n">
+        <v>200501</v>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 흙 묻은 유물 — 판정당 0.2% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="19" t="n">
+        <v>200502</v>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 조개 박힌 유물 — 판정당 0.5% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="19" t="n">
+        <v>200503</v>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 산호 엉긴 유물 — 판정당 0.4% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="19" t="n">
+        <v>200504</v>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>100064</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 봉인된 유물 — 판정당 0.15% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="19" t="n">
+        <v>200505</v>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 황금 띠 유물 — 판정당 0.015% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="19" t="n">
+        <v>200506</v>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>100066</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>발굴 Lv5 왕의 유물 — 판정당 0.0015% · 상자 대신 (테스트값 — T-150)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
